--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10158,6 +10158,66 @@
         <v>392.28</v>
       </c>
       <c r="H324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>409.15</v>
+      </c>
+      <c r="C325" t="n">
+        <v>398.55</v>
+      </c>
+      <c r="D325" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="E325" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="F325" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="G325" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>407.53</v>
+      </c>
+      <c r="C326" t="n">
+        <v>398.55</v>
+      </c>
+      <c r="D326" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="E326" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="F326" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="G326" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="H326" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10174,7 +10234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13507,6 +13567,26 @@
       </c>
       <c r="B333" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -13675,28 +13755,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09989155113708377</v>
+        <v>-0.1039953542315078</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04004765186392512</v>
+        <v>0.04360238591863741</v>
       </c>
       <c r="M2" t="n">
-        <v>2.787253957901399</v>
+        <v>2.790081332357416</v>
       </c>
       <c r="N2" t="n">
-        <v>12.87449306563543</v>
+        <v>12.86548412969385</v>
       </c>
       <c r="O2" t="n">
-        <v>3.58810438332491</v>
+        <v>3.586848774299504</v>
       </c>
       <c r="P2" t="n">
-        <v>414.2681707147291</v>
+        <v>414.3105330211454</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13757,28 +13837,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07731075118188685</v>
+        <v>-0.07969959629052775</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02342871937177127</v>
+        <v>0.02515549719408905</v>
       </c>
       <c r="M3" t="n">
-        <v>2.761096354885953</v>
+        <v>2.756105966763498</v>
       </c>
       <c r="N3" t="n">
-        <v>13.41019797111984</v>
+        <v>13.35010591727256</v>
       </c>
       <c r="O3" t="n">
-        <v>3.661993715330467</v>
+        <v>3.653779675524039</v>
       </c>
       <c r="P3" t="n">
-        <v>402.5027123180501</v>
+        <v>402.5273687165513</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -13839,28 +13919,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06573880137465646</v>
+        <v>-0.0708003975832793</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0151655465299062</v>
+        <v>0.0176696319601215</v>
       </c>
       <c r="M4" t="n">
-        <v>2.844270671672561</v>
+        <v>2.853454243482141</v>
       </c>
       <c r="N4" t="n">
-        <v>15.10597409353079</v>
+        <v>15.11372396983168</v>
       </c>
       <c r="O4" t="n">
-        <v>3.886640463630613</v>
+        <v>3.887637324884059</v>
       </c>
       <c r="P4" t="n">
-        <v>388.9894412788894</v>
+        <v>389.0416844103331</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -13921,28 +14001,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1095561271081724</v>
+        <v>-0.1178310770453426</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05190001771233654</v>
+        <v>0.05905046011585879</v>
       </c>
       <c r="M5" t="n">
-        <v>2.692428771972223</v>
+        <v>2.718119230479175</v>
       </c>
       <c r="N5" t="n">
-        <v>11.80211875204148</v>
+        <v>11.99866062757454</v>
       </c>
       <c r="O5" t="n">
-        <v>3.435421189904009</v>
+        <v>3.463908287985486</v>
       </c>
       <c r="P5" t="n">
-        <v>386.9732920403382</v>
+        <v>387.0587017171923</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14003,28 +14083,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07016648833435808</v>
+        <v>-0.07947319208646923</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02487202874992489</v>
+        <v>0.03111470334550004</v>
       </c>
       <c r="M6" t="n">
-        <v>2.472492098005428</v>
+        <v>2.502391259343018</v>
       </c>
       <c r="N6" t="n">
-        <v>10.38986469454156</v>
+        <v>10.66640430737119</v>
       </c>
       <c r="O6" t="n">
-        <v>3.223331303875164</v>
+        <v>3.265946158063723</v>
       </c>
       <c r="P6" t="n">
-        <v>385.5359141748949</v>
+        <v>385.63197307504</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14085,28 +14165,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1088292256742549</v>
+        <v>-0.1166092779409395</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04552471838402339</v>
+        <v>0.05171735730507643</v>
       </c>
       <c r="M7" t="n">
-        <v>2.91873384382109</v>
+        <v>2.940713722035008</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3662168126773</v>
+        <v>13.52189986647967</v>
       </c>
       <c r="O7" t="n">
-        <v>3.655983699728063</v>
+        <v>3.677213600877663</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0952522168591</v>
+        <v>401.1755538201066</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14148,7 +14228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27759,6 +27839,90 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.44068440677324,174.39492921838118</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.44120701082188,174.39550811507266</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.4416714571429,174.39617521987213</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.44206989163409,174.39692251948628</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-35.44240315797978,174.39772708664205</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-35.44268112297636,174.3985720053201</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-35.44069566803936,174.39491785554162</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-35.44120701082188,174.39550811507266</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-35.4416714571429,174.39617521987213</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-35.44206989163409,174.39692251948628</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-35.44240315797978,174.39772708664205</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-35.44268112297636,174.3985720053201</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:H328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10220,6 +10220,66 @@
       <c r="H326" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>406.49</v>
+      </c>
+      <c r="C327" t="n">
+        <v>397.71</v>
+      </c>
+      <c r="D327" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="E327" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="F327" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="G327" t="n">
+        <v>390.92</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>405.96</v>
+      </c>
+      <c r="C328" t="n">
+        <v>398.07</v>
+      </c>
+      <c r="D328" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="E328" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="F328" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="G328" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B335"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13587,6 +13647,26 @@
       </c>
       <c r="B335" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -13755,28 +13835,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1039953542315078</v>
+        <v>-0.1105532839877661</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04360238591863741</v>
+        <v>0.04900748834477131</v>
       </c>
       <c r="M2" t="n">
-        <v>2.790081332357416</v>
+        <v>2.804878054511904</v>
       </c>
       <c r="N2" t="n">
-        <v>12.86548412969385</v>
+        <v>12.95887063860556</v>
       </c>
       <c r="O2" t="n">
-        <v>3.586848774299504</v>
+        <v>3.599843140833439</v>
       </c>
       <c r="P2" t="n">
-        <v>414.3105330211454</v>
+        <v>414.3785151635016</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13837,28 +13917,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07969959629052775</v>
+        <v>-0.0828126180594022</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02515549719408905</v>
+        <v>0.02738735267753045</v>
       </c>
       <c r="M3" t="n">
-        <v>2.756105966763498</v>
+        <v>2.755295734643337</v>
       </c>
       <c r="N3" t="n">
-        <v>13.35010591727256</v>
+        <v>13.30736578520853</v>
       </c>
       <c r="O3" t="n">
-        <v>3.653779675524039</v>
+        <v>3.647926230779417</v>
       </c>
       <c r="P3" t="n">
-        <v>402.5273687165513</v>
+        <v>402.5596357718997</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -13919,28 +13999,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0708003975832793</v>
+        <v>-0.0776289589481622</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0176696319601215</v>
+        <v>0.02119299213477932</v>
       </c>
       <c r="M4" t="n">
-        <v>2.853454243482141</v>
+        <v>2.872440172868623</v>
       </c>
       <c r="N4" t="n">
-        <v>15.11372396983168</v>
+        <v>15.20762952880392</v>
       </c>
       <c r="O4" t="n">
-        <v>3.887637324884059</v>
+        <v>3.899696081594554</v>
       </c>
       <c r="P4" t="n">
-        <v>389.0416844103331</v>
+        <v>389.1124667201963</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -14001,28 +14081,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1178310770453426</v>
+        <v>-0.1273708691644598</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05905046011585879</v>
+        <v>0.06727725227446546</v>
       </c>
       <c r="M5" t="n">
-        <v>2.718119230479175</v>
+        <v>2.750772897075675</v>
       </c>
       <c r="N5" t="n">
-        <v>11.99866062757454</v>
+        <v>12.28948700509238</v>
       </c>
       <c r="O5" t="n">
-        <v>3.463908287985486</v>
+        <v>3.505636462198039</v>
       </c>
       <c r="P5" t="n">
-        <v>387.0587017171923</v>
+        <v>387.1575859637061</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14083,28 +14163,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07947319208646923</v>
+        <v>-0.08827073337642861</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03111470334550004</v>
+        <v>0.03755404418692898</v>
       </c>
       <c r="M6" t="n">
-        <v>2.502391259343018</v>
+        <v>2.529776649777442</v>
       </c>
       <c r="N6" t="n">
-        <v>10.66640430737119</v>
+        <v>10.91094372060745</v>
       </c>
       <c r="O6" t="n">
-        <v>3.265946158063723</v>
+        <v>3.303171766742906</v>
       </c>
       <c r="P6" t="n">
-        <v>385.63197307504</v>
+        <v>385.7231634567963</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14165,28 +14245,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1166092779409395</v>
+        <v>-0.1251998000796639</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05171735730507643</v>
+        <v>0.05870098382997591</v>
       </c>
       <c r="M7" t="n">
-        <v>2.940713722035008</v>
+        <v>2.967473789802879</v>
       </c>
       <c r="N7" t="n">
-        <v>13.52189986647967</v>
+        <v>13.73405247576978</v>
       </c>
       <c r="O7" t="n">
-        <v>3.677213600877663</v>
+        <v>3.705948255948777</v>
       </c>
       <c r="P7" t="n">
-        <v>401.1755538201066</v>
+        <v>401.2646002419734</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14228,7 +14308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:H328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27923,6 +28003,90 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-35.44070289749361,174.39491056087752</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-35.44121327079481,174.39550290816084</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-35.441685124586456,174.3961660400763</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-35.442082812552066,174.39691444054964</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-35.442404418963214,174.3977262308754</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-35.442689025308475,174.39856584006316</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-35.44070658173456,174.39490684340396</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-35.4412105879493,174.39550513969456</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-35.44168259650447,174.39616773807344</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-35.442076953999255,174.3969181036703</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-35.442398980972165,174.397729921369</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-35.44268628988585,174.39856797419068</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H328"/>
+  <dimension ref="A1:H329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10278,6 +10278,36 @@
         <v>391.28</v>
       </c>
       <c r="H328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>404.92</v>
+      </c>
+      <c r="C329" t="n">
+        <v>398.63</v>
+      </c>
+      <c r="D329" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="E329" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="F329" t="n">
+        <v>380.32</v>
+      </c>
+      <c r="G329" t="n">
+        <v>394.76</v>
+      </c>
+      <c r="H329" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10294,7 +10324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:B338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13667,6 +13697,16 @@
       </c>
       <c r="B337" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -13835,28 +13875,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1105532839877661</v>
+        <v>-0.1145955915228631</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04900748834477131</v>
+        <v>0.05232047736339895</v>
       </c>
       <c r="M2" t="n">
-        <v>2.804878054511904</v>
+        <v>2.816265400491408</v>
       </c>
       <c r="N2" t="n">
-        <v>12.95887063860556</v>
+        <v>13.04765389005506</v>
       </c>
       <c r="O2" t="n">
-        <v>3.599843140833439</v>
+        <v>3.612153635998206</v>
       </c>
       <c r="P2" t="n">
-        <v>414.3785151635016</v>
+        <v>414.4208517380738</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13917,28 +13957,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0828126180594022</v>
+        <v>-0.08388710656918449</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02738735267753045</v>
+        <v>0.02825446942063647</v>
       </c>
       <c r="M3" t="n">
-        <v>2.755295734643337</v>
+        <v>2.752298149899306</v>
       </c>
       <c r="N3" t="n">
-        <v>13.30736578520853</v>
+        <v>13.27585906022176</v>
       </c>
       <c r="O3" t="n">
-        <v>3.647926230779417</v>
+        <v>3.643605228372273</v>
       </c>
       <c r="P3" t="n">
-        <v>402.5596357718997</v>
+        <v>402.5708892855244</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -13999,28 +14039,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0776289589481622</v>
+        <v>-0.08006573370908486</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02119299213477932</v>
+        <v>0.0225997592424283</v>
       </c>
       <c r="M4" t="n">
-        <v>2.872440172868623</v>
+        <v>2.876793730386197</v>
       </c>
       <c r="N4" t="n">
-        <v>15.20762952880392</v>
+        <v>15.20788473927053</v>
       </c>
       <c r="O4" t="n">
-        <v>3.899696081594554</v>
+        <v>3.899728803297805</v>
       </c>
       <c r="P4" t="n">
-        <v>389.1124667201963</v>
+        <v>389.1379879591137</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -14081,28 +14121,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1273708691644598</v>
+        <v>-0.1313513260344669</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06727725227446546</v>
+        <v>0.07103618956915581</v>
       </c>
       <c r="M5" t="n">
-        <v>2.750772897075675</v>
+        <v>2.762981264410056</v>
       </c>
       <c r="N5" t="n">
-        <v>12.28948700509238</v>
+        <v>12.37641514687446</v>
       </c>
       <c r="O5" t="n">
-        <v>3.505636462198039</v>
+        <v>3.518012954335793</v>
       </c>
       <c r="P5" t="n">
-        <v>387.1575859637061</v>
+        <v>387.1992747534989</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14163,28 +14203,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08827073337642861</v>
+        <v>-0.09016551174707747</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03755404418692898</v>
+        <v>0.03928459672291318</v>
       </c>
       <c r="M6" t="n">
-        <v>2.529776649777442</v>
+        <v>2.53118380409809</v>
       </c>
       <c r="N6" t="n">
-        <v>10.91094372060745</v>
+        <v>10.90586622374304</v>
       </c>
       <c r="O6" t="n">
-        <v>3.303171766742906</v>
+        <v>3.302403098312355</v>
       </c>
       <c r="P6" t="n">
-        <v>385.7231634567963</v>
+        <v>385.7430081680386</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14245,28 +14285,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1251998000796639</v>
+        <v>-0.127174631669328</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05870098382997591</v>
+        <v>0.06072372453064667</v>
       </c>
       <c r="M7" t="n">
-        <v>2.967473789802879</v>
+        <v>2.968644226614234</v>
       </c>
       <c r="N7" t="n">
-        <v>13.73405247576978</v>
+        <v>13.7228000705344</v>
       </c>
       <c r="O7" t="n">
-        <v>3.705948255948777</v>
+        <v>3.70442979020178</v>
       </c>
       <c r="P7" t="n">
-        <v>401.2646002419734</v>
+        <v>401.2852833800417</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14308,7 +14348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H328"/>
+  <dimension ref="A1:H329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28087,6 +28127,48 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-35.44071381118818,174.39489954873792</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-35.44120641463397,174.395508610969</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-35.4416719311583,174.39617490149777</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-35.442070373158984,174.39692221840795</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-35.44237053003183,174.39774922959563</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-35.44265984746539,174.39858860408285</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H329"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10310,6 +10310,36 @@
       <c r="H329" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>402.6</v>
+      </c>
+      <c r="C330" t="n">
+        <v>396.57</v>
+      </c>
+      <c r="D330" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="E330" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="F330" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="G330" t="n">
+        <v>392.1</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B338"/>
+  <dimension ref="A1:B339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13707,6 +13737,16 @@
       </c>
       <c r="B338" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -13875,28 +13915,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1145955915228631</v>
+        <v>-0.1200117042182242</v>
       </c>
       <c r="J2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05232047736339895</v>
+        <v>0.0565212545314594</v>
       </c>
       <c r="M2" t="n">
-        <v>2.816265400491408</v>
+        <v>2.834500041115527</v>
       </c>
       <c r="N2" t="n">
-        <v>13.04765389005506</v>
+        <v>13.23951334478508</v>
       </c>
       <c r="O2" t="n">
-        <v>3.612153635998206</v>
+        <v>3.638614206643111</v>
       </c>
       <c r="P2" t="n">
-        <v>414.4208517380738</v>
+        <v>414.4777326235421</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13957,28 +13997,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08388710656918449</v>
+        <v>-0.08621512413944958</v>
       </c>
       <c r="J3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02825446942063647</v>
+        <v>0.02990500029670573</v>
       </c>
       <c r="M3" t="n">
-        <v>2.752298149899306</v>
+        <v>2.755643232157713</v>
       </c>
       <c r="N3" t="n">
-        <v>13.27585906022176</v>
+        <v>13.27828109974459</v>
       </c>
       <c r="O3" t="n">
-        <v>3.643605228372273</v>
+        <v>3.643937581757486</v>
       </c>
       <c r="P3" t="n">
-        <v>402.5708892855244</v>
+        <v>402.5953384999759</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -14039,28 +14079,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08006573370908486</v>
+        <v>-0.0832111735620276</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0225997592424283</v>
+        <v>0.02440943052889777</v>
       </c>
       <c r="M4" t="n">
-        <v>2.876793730386197</v>
+        <v>2.88483506497309</v>
       </c>
       <c r="N4" t="n">
-        <v>15.20788473927053</v>
+        <v>15.23974597290235</v>
       </c>
       <c r="O4" t="n">
-        <v>3.899728803297805</v>
+        <v>3.903811723546917</v>
       </c>
       <c r="P4" t="n">
-        <v>389.1379879591137</v>
+        <v>389.1710218736731</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -14121,28 +14161,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1313513260344669</v>
+        <v>-0.1356904547032209</v>
       </c>
       <c r="J5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07103618956915581</v>
+        <v>0.07509777113382476</v>
       </c>
       <c r="M5" t="n">
-        <v>2.762981264410056</v>
+        <v>2.777158886824679</v>
       </c>
       <c r="N5" t="n">
-        <v>12.37641514687446</v>
+        <v>12.4873953521656</v>
       </c>
       <c r="O5" t="n">
-        <v>3.518012954335793</v>
+        <v>3.533750889941961</v>
       </c>
       <c r="P5" t="n">
-        <v>387.1992747534989</v>
+        <v>387.2448449797334</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14203,28 +14243,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09016551174707747</v>
+        <v>-0.09258617587625612</v>
       </c>
       <c r="J6" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03928459672291318</v>
+        <v>0.04144136253389541</v>
       </c>
       <c r="M6" t="n">
-        <v>2.53118380409809</v>
+        <v>2.535410645690207</v>
       </c>
       <c r="N6" t="n">
-        <v>10.90586622374304</v>
+        <v>10.91896414451763</v>
       </c>
       <c r="O6" t="n">
-        <v>3.302403098312355</v>
+        <v>3.304385592590191</v>
       </c>
       <c r="P6" t="n">
-        <v>385.7430081680386</v>
+        <v>385.7684303715328</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14285,28 +14325,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.127174631669328</v>
+        <v>-0.1307586738827372</v>
       </c>
       <c r="J7" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06072372453064667</v>
+        <v>0.06394682152732312</v>
       </c>
       <c r="M7" t="n">
-        <v>2.968644226614234</v>
+        <v>2.978846019580778</v>
       </c>
       <c r="N7" t="n">
-        <v>13.7228000705344</v>
+        <v>13.7824701977378</v>
       </c>
       <c r="O7" t="n">
-        <v>3.70442979020178</v>
+        <v>3.712474942371705</v>
       </c>
       <c r="P7" t="n">
-        <v>401.2852833800417</v>
+        <v>401.3229235670394</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14348,7 +14388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H329"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28169,6 +28209,48 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-35.440729938429364,174.39488327601666</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-35.441221766472054,174.39549584163635</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-35.441681490468575,174.39616848094718</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-35.442075830441176,174.39691880618653</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-35.44237762306432,174.39774441591157</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-35.44268005920087,174.39857283525845</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10340,6 +10340,66 @@
       <c r="H330" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>403.78</v>
+      </c>
+      <c r="C331" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D331" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="E331" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="F331" t="n">
+        <v>380.24</v>
+      </c>
+      <c r="G331" t="n">
+        <v>392.37</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>407.21</v>
+      </c>
+      <c r="C332" t="n">
+        <v>397.79</v>
+      </c>
+      <c r="D332" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="E332" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="F332" t="n">
+        <v>381.11</v>
+      </c>
+      <c r="G332" t="n">
+        <v>391.66</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B339"/>
+  <dimension ref="A1:B341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13747,6 +13807,26 @@
       </c>
       <c r="B339" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -13915,28 +13995,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1200117042182242</v>
+        <v>-0.127065047350586</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0565212545314594</v>
+        <v>0.06279063848392308</v>
       </c>
       <c r="M2" t="n">
-        <v>2.834500041115527</v>
+        <v>2.85241672602276</v>
       </c>
       <c r="N2" t="n">
-        <v>13.23951334478508</v>
+        <v>13.37500096958882</v>
       </c>
       <c r="O2" t="n">
-        <v>3.638614206643111</v>
+        <v>3.657184842141401</v>
       </c>
       <c r="P2" t="n">
-        <v>414.4777326235421</v>
+        <v>414.5521010548143</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13997,28 +14077,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08621512413944958</v>
+        <v>-0.08926602062077148</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02990500029670573</v>
+        <v>0.03233499992192568</v>
       </c>
       <c r="M3" t="n">
-        <v>2.755643232157713</v>
+        <v>2.754164819140027</v>
       </c>
       <c r="N3" t="n">
-        <v>13.27828109974459</v>
+        <v>13.23501435519441</v>
       </c>
       <c r="O3" t="n">
-        <v>3.643937581757486</v>
+        <v>3.637995925670397</v>
       </c>
       <c r="P3" t="n">
-        <v>402.5953384999759</v>
+        <v>402.6275106981628</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -14079,28 +14159,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0832111735620276</v>
+        <v>-0.08881086978376401</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02440943052889777</v>
+        <v>0.02786323520660616</v>
       </c>
       <c r="M4" t="n">
-        <v>2.88483506497309</v>
+        <v>2.896994324787464</v>
       </c>
       <c r="N4" t="n">
-        <v>15.23974597290235</v>
+        <v>15.27312730477838</v>
       </c>
       <c r="O4" t="n">
-        <v>3.903811723546917</v>
+        <v>3.908084864070684</v>
       </c>
       <c r="P4" t="n">
-        <v>389.1710218736731</v>
+        <v>389.2300692066547</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -14161,28 +14241,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1356904547032209</v>
+        <v>-0.14342329748882</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07509777113382476</v>
+        <v>0.08278001556712766</v>
       </c>
       <c r="M5" t="n">
-        <v>2.777158886824679</v>
+        <v>2.800873780157953</v>
       </c>
       <c r="N5" t="n">
-        <v>12.4873953521656</v>
+        <v>12.64990632558938</v>
       </c>
       <c r="O5" t="n">
-        <v>3.533750889941961</v>
+        <v>3.556670679946258</v>
       </c>
       <c r="P5" t="n">
-        <v>387.2448449797334</v>
+        <v>387.3263873098893</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14243,28 +14323,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09258617587625612</v>
+        <v>-0.09578788204656334</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04144136253389541</v>
+        <v>0.04465400640912875</v>
       </c>
       <c r="M6" t="n">
-        <v>2.535410645690207</v>
+        <v>2.535929914555972</v>
       </c>
       <c r="N6" t="n">
-        <v>10.91896414451763</v>
+        <v>10.89485101809684</v>
       </c>
       <c r="O6" t="n">
-        <v>3.304385592590191</v>
+        <v>3.300734920907287</v>
       </c>
       <c r="P6" t="n">
-        <v>385.7684303715328</v>
+        <v>385.8021902785825</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14325,28 +14405,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1307586738827372</v>
+        <v>-0.13785881780278</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06394682152732312</v>
+        <v>0.07053178200377652</v>
       </c>
       <c r="M7" t="n">
-        <v>2.978846019580778</v>
+        <v>2.999216226984311</v>
       </c>
       <c r="N7" t="n">
-        <v>13.7824701977378</v>
+        <v>13.90012435443345</v>
       </c>
       <c r="O7" t="n">
-        <v>3.712474942371705</v>
+        <v>3.728287053652581</v>
       </c>
       <c r="P7" t="n">
-        <v>401.3229235670394</v>
+        <v>401.3977977305129</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14388,7 +14468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28251,6 +28331,90 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-35.440721735781096,174.39489155266017</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-35.44121260008344,174.3955034660443</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-35.4416810164532,174.3961687993216</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-35.442073182054244,174.39692046211758</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-35.44237116052361,174.39774880171265</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-35.44267800763382,174.39857443585376</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-35.440697892486874,174.39491561102972</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-35.44121267460693,174.39550340405722</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-35.44167485425321,174.39617293818907</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-35.44206868782185,174.39692327218214</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-35.44236430392538,174.39775345493987</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-35.442683402495284,174.39857022688074</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
